--- a/Team-Data/2007-08/11-8-2007-08.xlsx
+++ b/Team-Data/2007-08/11-8-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
@@ -757,13 +824,13 @@
         <v>23</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>19</v>
       </c>
       <c r="AL2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM2" t="n">
         <v>24</v>
@@ -772,7 +839,7 @@
         <v>23</v>
       </c>
       <c r="AO2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
@@ -793,13 +860,13 @@
         <v>26</v>
       </c>
       <c r="AV2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW2" t="n">
         <v>3</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY2" t="n">
         <v>30</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>16.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF3" t="n">
         <v>1</v>
@@ -945,7 +1012,7 @@
         <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM3" t="n">
         <v>5</v>
@@ -984,16 +1051,16 @@
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
         <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>13</v>
@@ -1121,10 +1188,10 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
         <v>27</v>
@@ -1145,7 +1212,7 @@
         <v>29</v>
       </c>
       <c r="AR4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1169,10 +1236,10 @@
         <v>17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -1207,100 +1274,100 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="I5" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="J5" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.39</v>
+        <v>0.373</v>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>17.2</v>
+        <v>19.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.267</v>
+        <v>0.286</v>
       </c>
       <c r="O5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P5" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="R5" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="S5" t="n">
-        <v>29.2</v>
+        <v>28.5</v>
       </c>
       <c r="T5" t="n">
-        <v>43.4</v>
+        <v>42.5</v>
       </c>
       <c r="U5" t="n">
-        <v>20.8</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="X5" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.8</v>
+        <v>24.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>89.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5.6</v>
+        <v>-8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG5" t="n">
         <v>25</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1309,58 +1376,58 @@
         <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AM5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
         <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AU5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV5" t="n">
         <v>17</v>
       </c>
-      <c r="AV5" t="n">
-        <v>16</v>
-      </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1549,7 @@
         <v>7</v>
       </c>
       <c r="AI6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ6" t="n">
         <v>10</v>
@@ -1491,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
         <v>14</v>
@@ -1503,10 +1570,10 @@
         <v>24</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR6" t="n">
         <v>8</v>
@@ -1518,16 +1585,16 @@
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV6" t="n">
         <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -1571,118 +1638,118 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>38.2</v>
+        <v>37.3</v>
       </c>
       <c r="J7" t="n">
-        <v>75.8</v>
+        <v>73.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.504</v>
+        <v>0.505</v>
       </c>
       <c r="L7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.6</v>
+        <v>18.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.388</v>
+        <v>0.378</v>
       </c>
       <c r="O7" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="P7" t="n">
-        <v>26.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.879</v>
+        <v>0.882</v>
       </c>
       <c r="R7" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>30.3</v>
       </c>
       <c r="T7" t="n">
-        <v>39.4</v>
+        <v>37</v>
       </c>
       <c r="U7" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="V7" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W7" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>22.6</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="AB7" t="n">
-        <v>107.2</v>
+        <v>104</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
         <v>7</v>
       </c>
       <c r="AI7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AN7" t="n">
         <v>11</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
         <v>17</v>
@@ -1694,19 +1761,19 @@
         <v>30</v>
       </c>
       <c r="AS7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
         <v>2</v>
@@ -1715,16 +1782,16 @@
         <v>2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
         <v>17</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1922,7 @@
         <v>13</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM8" t="n">
         <v>14</v>
@@ -1864,7 +1931,7 @@
         <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP8" t="n">
         <v>6</v>
@@ -1873,7 +1940,7 @@
         <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
         <v>9</v>
@@ -1882,25 +1949,25 @@
         <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA8" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>12</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -1935,103 +2002,103 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.75</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>35.8</v>
+        <v>37</v>
       </c>
       <c r="J9" t="n">
-        <v>76.5</v>
+        <v>78</v>
       </c>
       <c r="K9" t="n">
-        <v>0.467</v>
+        <v>0.474</v>
       </c>
       <c r="L9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="N9" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="O9" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
-        <v>27.8</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.748</v>
+        <v>0.741</v>
       </c>
       <c r="R9" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="S9" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="T9" t="n">
-        <v>39.8</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
-        <v>21</v>
+        <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="X9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE9" t="n">
         <v>6</v>
       </c>
-      <c r="Y9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>98</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>8</v>
-      </c>
       <c r="AF9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
         <v>7</v>
       </c>
       <c r="AI9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
         <v>6</v>
@@ -2043,43 +2110,43 @@
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
         <v>23</v>
       </c>
       <c r="AT9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="n">
         <v>6</v>
       </c>
-      <c r="AW9" t="n">
-        <v>12</v>
-      </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BA9" t="n">
         <v>25</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -2117,13 +2184,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2132,112 +2199,112 @@
         <v>48</v>
       </c>
       <c r="I10" t="n">
-        <v>39.8</v>
+        <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>85.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.463</v>
+        <v>0.455</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="M10" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.344</v>
+        <v>0.321</v>
       </c>
       <c r="O10" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.671</v>
+        <v>0.708</v>
       </c>
       <c r="R10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S10" t="n">
-        <v>27.6</v>
+        <v>27</v>
       </c>
       <c r="T10" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="U10" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>15.8</v>
       </c>
       <c r="W10" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="X10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y10" t="n">
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>24</v>
+        <v>22.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>107.8</v>
+        <v>106</v>
       </c>
       <c r="AC10" t="n">
-        <v>-11.8</v>
+        <v>-13.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH10" t="n">
         <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AK10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL10" t="n">
         <v>7</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>5</v>
       </c>
       <c r="AM10" t="n">
         <v>2</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AR10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS10" t="n">
         <v>29</v>
@@ -2246,16 +2313,16 @@
         <v>29</v>
       </c>
       <c r="AU10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX10" t="n">
         <v>11</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
@@ -2264,13 +2331,13 @@
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -2383,16 +2450,16 @@
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH11" t="n">
         <v>7</v>
       </c>
       <c r="AI11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
@@ -2401,7 +2468,7 @@
         <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM11" t="n">
         <v>8</v>
@@ -2416,7 +2483,7 @@
         <v>22</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
         <v>4</v>
@@ -2428,13 +2495,13 @@
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
         <v>14</v>
@@ -2443,7 +2510,7 @@
         <v>21</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>22</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -2559,31 +2626,31 @@
         <v>1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG12" t="n">
         <v>8</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>3</v>
       </c>
-      <c r="AG12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2</v>
-      </c>
       <c r="AI12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM12" t="n">
         <v>9</v>
@@ -2592,10 +2659,10 @@
         <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ12" t="n">
         <v>6</v>
@@ -2613,13 +2680,13 @@
         <v>13</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY12" t="n">
         <v>13</v>
@@ -2628,10 +2695,10 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
         <v>16</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>10.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2756,7 +2823,7 @@
         <v>7</v>
       </c>
       <c r="AI13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2768,7 +2835,7 @@
         <v>9</v>
       </c>
       <c r="AM13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN13" t="n">
         <v>3</v>
@@ -2777,7 +2844,7 @@
         <v>3</v>
       </c>
       <c r="AP13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
         <v>9</v>
@@ -2789,16 +2856,16 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="n">
         <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="n">
         <v>17</v>
@@ -2807,16 +2874,16 @@
         <v>27</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB13" t="n">
         <v>2</v>
       </c>
       <c r="BC13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>13</v>
@@ -2944,19 +3011,19 @@
         <v>14</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="n">
         <v>23</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
@@ -2989,10 +3056,10 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-2</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
@@ -3144,10 +3211,10 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS15" t="n">
         <v>11</v>
@@ -3156,7 +3223,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>28</v>
@@ -3168,7 +3235,7 @@
         <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ15" t="n">
         <v>9</v>
@@ -3177,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -3287,22 +3354,22 @@
         <v>-6.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH16" t="n">
         <v>7</v>
       </c>
       <c r="AI16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>20</v>
@@ -3311,7 +3378,7 @@
         <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM16" t="n">
         <v>26</v>
@@ -3329,7 +3396,7 @@
         <v>30</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
         <v>17</v>
@@ -3338,13 +3405,13 @@
         <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
         <v>17</v>
@@ -3362,7 +3429,7 @@
         <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
         <v>13</v>
@@ -3484,7 +3551,7 @@
         <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
@@ -3493,13 +3560,13 @@
         <v>15</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
@@ -3520,7 +3587,7 @@
         <v>7</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV17" t="n">
         <v>18</v>
@@ -3529,16 +3596,16 @@
         <v>25</v>
       </c>
       <c r="AX17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ17" t="n">
         <v>25</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
         <v>24</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3718,22 @@
         <v>-6.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF18" t="n">
         <v>20</v>
       </c>
       <c r="AG18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH18" t="n">
         <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ18" t="n">
         <v>6</v>
@@ -3675,10 +3742,10 @@
         <v>17</v>
       </c>
       <c r="AL18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="n">
         <v>6</v>
@@ -3690,7 +3757,7 @@
         <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
         <v>13</v>
@@ -3702,13 +3769,13 @@
         <v>22</v>
       </c>
       <c r="AU18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX18" t="n">
         <v>23</v>
@@ -3726,7 +3793,7 @@
         <v>18</v>
       </c>
       <c r="BC18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -3755,97 +3822,97 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H19" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="I19" t="n">
-        <v>30.6</v>
+        <v>31.3</v>
       </c>
       <c r="J19" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K19" t="n">
-        <v>0.403</v>
+        <v>0.406</v>
       </c>
       <c r="L19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="M19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.31</v>
+        <v>0.346</v>
       </c>
       <c r="O19" t="n">
-        <v>22.2</v>
+        <v>21</v>
       </c>
       <c r="P19" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="S19" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T19" t="n">
-        <v>42.6</v>
+        <v>43.5</v>
       </c>
       <c r="U19" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="V19" t="n">
-        <v>17.8</v>
+        <v>18.3</v>
       </c>
       <c r="W19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y19" t="n">
         <v>4.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>89.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH19" t="n">
         <v>3</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
@@ -3854,55 +3921,55 @@
         <v>26</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AO19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>5</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU19" t="n">
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>8</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
         <v>27</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -4021,10 +4088,10 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
         <v>7</v>
@@ -4036,7 +4103,7 @@
         <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL20" t="n">
         <v>3</v>
@@ -4057,7 +4124,7 @@
         <v>4</v>
       </c>
       <c r="AR20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS20" t="n">
         <v>4</v>
@@ -4066,10 +4133,10 @@
         <v>7</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
         <v>18</v>
@@ -4078,7 +4145,7 @@
         <v>14</v>
       </c>
       <c r="AY20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ20" t="n">
         <v>8</v>
@@ -4090,7 +4157,7 @@
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
         <v>13</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG21" t="n">
         <v>11</v>
@@ -4221,7 +4288,7 @@
         <v>5</v>
       </c>
       <c r="AL21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM21" t="n">
         <v>25</v>
@@ -4230,7 +4297,7 @@
         <v>2</v>
       </c>
       <c r="AO21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
         <v>7</v>
@@ -4242,16 +4309,16 @@
         <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT21" t="n">
         <v>19</v>
       </c>
       <c r="AU21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
         <v>26</v>
@@ -4269,7 +4336,7 @@
         <v>3</v>
       </c>
       <c r="BB21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC21" t="n">
         <v>15</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -4385,10 +4452,10 @@
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH22" t="n">
         <v>7</v>
@@ -4397,7 +4464,7 @@
         <v>24</v>
       </c>
       <c r="AJ22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK22" t="n">
         <v>12</v>
@@ -4412,13 +4479,13 @@
         <v>5</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
         <v>5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
         <v>27</v>
@@ -4430,22 +4497,22 @@
         <v>16</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV22" t="n">
         <v>2</v>
       </c>
       <c r="AW22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
       </c>
       <c r="AY22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>6</v>
       </c>
       <c r="BA22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>13</v>
@@ -4585,7 +4652,7 @@
         <v>22</v>
       </c>
       <c r="AL23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
@@ -4600,7 +4667,7 @@
         <v>8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>3</v>
@@ -4609,28 +4676,28 @@
         <v>13</v>
       </c>
       <c r="AT23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="n">
         <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW23" t="n">
         <v>3</v>
       </c>
       <c r="AX23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF24" t="n">
         <v>12</v>
@@ -4761,10 +4828,10 @@
         <v>5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL24" t="n">
         <v>5</v>
@@ -4782,22 +4849,22 @@
         <v>24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT24" t="n">
         <v>24</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>4</v>
       </c>
       <c r="AV24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>22</v>
@@ -4940,7 +5007,7 @@
         <v>7</v>
       </c>
       <c r="AI25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ25" t="n">
         <v>18</v>
@@ -4949,7 +5016,7 @@
         <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM25" t="n">
         <v>28</v>
@@ -4973,13 +5040,13 @@
         <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU25" t="n">
         <v>26</v>
       </c>
       <c r="AV25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW25" t="n">
         <v>30</v>
@@ -4991,13 +5058,13 @@
         <v>1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
         <v>26</v>
       </c>
       <c r="BB25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC25" t="n">
         <v>25</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-11.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>22</v>
@@ -5125,7 +5192,7 @@
         <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK26" t="n">
         <v>18</v>
@@ -5137,13 +5204,13 @@
         <v>30</v>
       </c>
       <c r="AN26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO26" t="n">
         <v>5</v>
       </c>
       <c r="AP26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5164,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX26" t="n">
         <v>29</v>
@@ -5182,7 +5249,7 @@
         <v>22</v>
       </c>
       <c r="BC26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -5295,10 +5362,10 @@
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
         <v>7</v>
@@ -5307,7 +5374,7 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK27" t="n">
         <v>10</v>
@@ -5337,10 +5404,10 @@
         <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
@@ -5352,10 +5419,10 @@
         <v>13</v>
       </c>
       <c r="AY27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -5474,22 +5541,22 @@
         <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH28" t="n">
         <v>7</v>
       </c>
       <c r="AI28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK28" t="n">
         <v>16</v>
@@ -5519,10 +5586,10 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>29</v>
@@ -5537,7 +5604,7 @@
         <v>16</v>
       </c>
       <c r="AZ28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA28" t="n">
         <v>27</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -5665,10 +5732,10 @@
         <v>19</v>
       </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="n">
         <v>10</v>
@@ -5695,16 +5762,16 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT29" t="n">
         <v>27</v>
       </c>
-      <c r="AT29" t="n">
-        <v>28</v>
-      </c>
       <c r="AU29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV29" t="n">
         <v>1</v>
@@ -5716,10 +5783,10 @@
         <v>27</v>
       </c>
       <c r="AY29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
         <v>12</v>
@@ -5859,7 +5926,7 @@
         <v>4</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>29</v>
@@ -5880,7 +5947,7 @@
         <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5889,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
@@ -5939,103 +6006,103 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="I31" t="n">
-        <v>31</v>
+        <v>31.7</v>
       </c>
       <c r="J31" t="n">
-        <v>85.3</v>
+        <v>89.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.364</v>
+        <v>0.354</v>
       </c>
       <c r="L31" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.221</v>
+        <v>0.203</v>
       </c>
       <c r="O31" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="P31" t="n">
-        <v>31.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.754</v>
+        <v>0.73</v>
       </c>
       <c r="R31" t="n">
-        <v>15.8</v>
+        <v>18.3</v>
       </c>
       <c r="S31" t="n">
-        <v>31.3</v>
+        <v>32</v>
       </c>
       <c r="T31" t="n">
-        <v>47</v>
+        <v>50.3</v>
       </c>
       <c r="U31" t="n">
-        <v>14.3</v>
+        <v>13.7</v>
       </c>
       <c r="V31" t="n">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="W31" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="X31" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Y31" t="n">
         <v>5.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-10.8</v>
+        <v>-13.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF31" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AG31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6044,7 +6111,7 @@
         <v>28</v>
       </c>
       <c r="AM31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AN31" t="n">
         <v>30</v>
@@ -6053,46 +6120,46 @@
         <v>4</v>
       </c>
       <c r="AP31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS31" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AT31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="n">
         <v>30</v>
       </c>
       <c r="AV31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY31" t="n">
         <v>20</v>
       </c>
-      <c r="AX31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>17</v>
-      </c>
       <c r="AZ31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
         <v>4</v>
       </c>
       <c r="BB31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-8-2007-08</t>
+          <t>2007-11-08</t>
         </is>
       </c>
     </row>
